--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Dhava.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Dhava.xlsx
@@ -5,10 +5,10 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wikha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDCB4227-FDB4-442C-8268-DC5A40C1DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{DDCB4227-FDB4-442C-8268-DC5A40C1DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C5C209-678A-4E08-8F95-48A7FB0B864A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,19 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -262,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -299,6 +312,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -319,35 +340,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -768,41 +766,41 @@
     <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="1"/>
-    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.26953125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -822,32 +820,32 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="4">
         <v>44770</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="5">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="4">
         <v>44770</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="5">
         <v>0.5</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="6">
         <v>0.99999999994179234</v>
       </c>
-      <c r="H4" s="19">
-        <v>2.25</v>
+      <c r="H4" s="1">
+        <v>1</v>
       </c>
       <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
@@ -858,32 +856,32 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="4">
         <v>44771</v>
       </c>
       <c r="C5" s="5">
         <v>0.5625</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="4">
         <v>44771</v>
       </c>
       <c r="E5" s="5">
-        <v>0.59375</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v>0.75</v>
+        <v>0.99999999994179234</v>
       </c>
       <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>3</v>
+        <v>1.9999999999417923</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0.75</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1340,14 +1338,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1949,14 +1947,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2445,14 +2443,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2939,18 +2937,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2964,6 +2950,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Dhava.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Dhava.xlsx
@@ -5,10 +5,10 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wikha\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{DDCB4227-FDB4-442C-8268-DC5A40C1DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C5C209-678A-4E08-8F95-48A7FB0B864A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDCB4227-FDB4-442C-8268-DC5A40C1DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,19 +18,6 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -275,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -312,14 +299,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -340,12 +319,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -766,41 +768,41 @@
     <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="1"/>
-    <col min="9" max="9" width="9.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
     <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -820,32 +822,32 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="20">
         <v>44770</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="20">
         <v>44770</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="21">
         <v>0.5</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="22">
         <v>0.99999999994179234</v>
       </c>
-      <c r="H4" s="1">
-        <v>1</v>
+      <c r="H4" s="19">
+        <v>2.25</v>
       </c>
       <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
@@ -856,32 +858,32 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="20">
         <v>44771</v>
       </c>
       <c r="C5" s="5">
         <v>0.5625</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="20">
         <v>44771</v>
       </c>
       <c r="E5" s="5">
-        <v>0.60416666666666663</v>
+        <v>0.59375</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>1.9999999999417923</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1338,14 +1340,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1947,14 +1949,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2443,14 +2445,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2937,6 +2939,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -2950,18 +2964,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
